--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487482_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487482_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>4.5666</v>
+        <v>4.7773</v>
       </c>
       <c r="E2" t="n">
-        <v>3.3987</v>
+        <v>3.6628</v>
       </c>
       <c r="F2" t="n">
-        <v>1.1679</v>
+        <v>1.1145</v>
       </c>
       <c r="G2" t="n">
         <v>0.5713</v>
@@ -610,13 +610,13 @@
         <v>1.9585</v>
       </c>
       <c r="S2" t="n">
-        <v>0.629</v>
+        <v>0.8396</v>
       </c>
       <c r="T2" t="n">
-        <v>0.2358</v>
+        <v>0.4999</v>
       </c>
       <c r="U2" t="n">
-        <v>0.3931</v>
+        <v>0.3397</v>
       </c>
       <c r="V2" t="n">
         <v>2.3871</v>
@@ -631,7 +631,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>J. RODRIGUEZ BUCETA</t>
+          <t>M. GIL RODRIGUEZ</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,73 +643,73 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>2.3352</v>
+        <v>1.9477</v>
       </c>
       <c r="E3" t="n">
-        <v>1.8893</v>
+        <v>0.2419</v>
       </c>
       <c r="F3" t="n">
-        <v>0.4459</v>
+        <v>1.7058</v>
       </c>
       <c r="G3" t="n">
-        <v>1.9204</v>
+        <v>1.8053</v>
       </c>
       <c r="H3" t="n">
-        <v>1.6472</v>
+        <v>1.8565</v>
       </c>
       <c r="I3" t="n">
-        <v>0.2733</v>
+        <v>-0.0512</v>
       </c>
       <c r="J3" t="n">
-        <v>2.3788</v>
+        <v>3.1221</v>
       </c>
       <c r="K3" t="n">
-        <v>2.2575</v>
+        <v>2.1232</v>
       </c>
       <c r="L3" t="n">
-        <v>0.1212</v>
+        <v>0.9989</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.4584</v>
+        <v>-1.3167</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.6104000000000001</v>
+        <v>-0.2667</v>
       </c>
       <c r="O3" t="n">
-        <v>0.152</v>
+        <v>-1.0501</v>
       </c>
       <c r="P3" t="n">
-        <v>0.1958</v>
+        <v>-0.1958</v>
       </c>
       <c r="Q3" t="n">
-        <v>-0.9792</v>
+        <v>-2.9377</v>
       </c>
       <c r="R3" t="n">
-        <v>1.1751</v>
+        <v>2.7419</v>
       </c>
       <c r="S3" t="n">
-        <v>1.4241</v>
+        <v>0.3267</v>
       </c>
       <c r="T3" t="n">
-        <v>1.1557</v>
+        <v>0.0576</v>
       </c>
       <c r="U3" t="n">
-        <v>0.2684</v>
+        <v>0.2691</v>
       </c>
       <c r="V3" t="n">
-        <v>-1.2051</v>
+        <v>0.0115</v>
       </c>
       <c r="W3" t="n">
-        <v>-0.6659</v>
+        <v>0</v>
       </c>
       <c r="X3" t="n">
-        <v>-0.5392</v>
+        <v>0.0115</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>M. GIL RODRIGUEZ</t>
+          <t>J. RODRIGUEZ BUCETA</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,67 +721,67 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>2.0843</v>
+        <v>1.6589</v>
       </c>
       <c r="E4" t="n">
-        <v>0.0043</v>
+        <v>1.4535</v>
       </c>
       <c r="F4" t="n">
-        <v>2.08</v>
+        <v>0.2053</v>
       </c>
       <c r="G4" t="n">
-        <v>1.8053</v>
+        <v>1.9204</v>
       </c>
       <c r="H4" t="n">
-        <v>1.8565</v>
+        <v>1.6472</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.0512</v>
+        <v>0.2733</v>
       </c>
       <c r="J4" t="n">
-        <v>3.1221</v>
+        <v>2.3788</v>
       </c>
       <c r="K4" t="n">
-        <v>2.1232</v>
+        <v>2.2575</v>
       </c>
       <c r="L4" t="n">
-        <v>0.9989</v>
+        <v>0.1212</v>
       </c>
       <c r="M4" t="n">
-        <v>-1.3167</v>
+        <v>-0.4584</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.2667</v>
+        <v>-0.6104000000000001</v>
       </c>
       <c r="O4" t="n">
-        <v>-1.0501</v>
+        <v>0.152</v>
       </c>
       <c r="P4" t="n">
-        <v>-0.1958</v>
+        <v>0.1958</v>
       </c>
       <c r="Q4" t="n">
-        <v>-2.9377</v>
+        <v>-0.9792</v>
       </c>
       <c r="R4" t="n">
-        <v>2.7419</v>
+        <v>1.1751</v>
       </c>
       <c r="S4" t="n">
-        <v>0.4633</v>
+        <v>0.7477</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.18</v>
+        <v>0.7199</v>
       </c>
       <c r="U4" t="n">
-        <v>0.6433</v>
+        <v>0.0278</v>
       </c>
       <c r="V4" t="n">
-        <v>0.0115</v>
+        <v>-1.2051</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>-0.6659</v>
       </c>
       <c r="X4" t="n">
-        <v>0.0115</v>
+        <v>-0.5392</v>
       </c>
     </row>
     <row r="5">
@@ -799,10 +799,10 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>0.5643</v>
+        <v>1.416</v>
       </c>
       <c r="E5" t="n">
-        <v>-1.2326</v>
+        <v>-0.381</v>
       </c>
       <c r="F5" t="n">
         <v>1.797</v>
@@ -844,10 +844,10 @@
         <v>2.7419</v>
       </c>
       <c r="S5" t="n">
-        <v>-1.525</v>
+        <v>-0.6734</v>
       </c>
       <c r="T5" t="n">
-        <v>-1.3662</v>
+        <v>-0.5145999999999999</v>
       </c>
       <c r="U5" t="n">
         <v>-0.1588</v>
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.2018</v>
+        <v>0.3147</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.0984</v>
+        <v>-0.039</v>
       </c>
       <c r="F6" t="n">
-        <v>0.3002</v>
+        <v>0.3537</v>
       </c>
       <c r="G6" t="n">
         <v>0.3621</v>
@@ -922,13 +922,13 @@
         <v>0.1958</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.3561</v>
+        <v>-0.2432</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.1188</v>
+        <v>-0.0594</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.2373</v>
+        <v>-0.1838</v>
       </c>
       <c r="V6" t="n">
         <v>0</v>
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.5671</v>
+        <v>-0.2509</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.5610000000000001</v>
+        <v>-0.4587</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.0061</v>
+        <v>0.2078</v>
       </c>
       <c r="G7" t="n">
         <v>-0.6679</v>
@@ -1000,13 +1000,13 @@
         <v>1.3709</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.2909</v>
+        <v>0.0253</v>
       </c>
       <c r="T7" t="n">
-        <v>0.0288</v>
+        <v>0.1312</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.3197</v>
+        <v>-0.1059</v>
       </c>
       <c r="V7" t="n">
         <v>0</v>
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-1.1446</v>
+        <v>-1.1665</v>
       </c>
       <c r="E8" t="n">
-        <v>-2.4666</v>
+        <v>-2.5954</v>
       </c>
       <c r="F8" t="n">
-        <v>1.322</v>
+        <v>1.4289</v>
       </c>
       <c r="G8" t="n">
         <v>-2.4503</v>
@@ -1078,13 +1078,13 @@
         <v>1.3709</v>
       </c>
       <c r="S8" t="n">
-        <v>0.2365</v>
+        <v>0.2147</v>
       </c>
       <c r="T8" t="n">
-        <v>0.2952</v>
+        <v>0.1664</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.0587</v>
+        <v>0.0482</v>
       </c>
       <c r="V8" t="n">
         <v>0.6774</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.6503</v>
+        <v>-2.4272</v>
       </c>
       <c r="E9" t="n">
-        <v>-2.0734</v>
+        <v>-3.0373</v>
       </c>
       <c r="F9" t="n">
-        <v>0.4231</v>
+        <v>0.6102</v>
       </c>
       <c r="G9" t="n">
         <v>-3.5058</v>
@@ -1156,13 +1156,13 @@
         <v>1.7626</v>
       </c>
       <c r="S9" t="n">
-        <v>0.7587</v>
+        <v>-0.0181</v>
       </c>
       <c r="T9" t="n">
-        <v>1.0369</v>
+        <v>0.07290000000000001</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.2781</v>
+        <v>-0.091</v>
       </c>
       <c r="V9" t="n">
         <v>-0.6659</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-3.6819</v>
+        <v>-2.9863</v>
       </c>
       <c r="E10" t="n">
-        <v>-1.3706</v>
+        <v>-0.5948</v>
       </c>
       <c r="F10" t="n">
-        <v>-2.3113</v>
+        <v>-2.3915</v>
       </c>
       <c r="G10" t="n">
         <v>-1.0235</v>
@@ -1234,13 +1234,13 @@
         <v>0.3917</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.6169</v>
+        <v>0.07870000000000001</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.4752</v>
+        <v>0.3005</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.1417</v>
+        <v>-0.2219</v>
       </c>
       <c r="V10" t="n">
         <v>-2.4332</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-4.1525</v>
+        <v>-3.5395</v>
       </c>
       <c r="E11" t="n">
-        <v>-5.2764</v>
+        <v>-4.8506</v>
       </c>
       <c r="F11" t="n">
-        <v>1.124</v>
+        <v>1.3111</v>
       </c>
       <c r="G11" t="n">
         <v>-0.6325</v>
@@ -1312,13 +1312,13 @@
         <v>0.9792</v>
       </c>
       <c r="S11" t="n">
-        <v>-1.2286</v>
+        <v>-0.6156</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.9504</v>
+        <v>-0.5246</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.2781</v>
+        <v>-0.091</v>
       </c>
       <c r="V11" t="n">
         <v>-0.3329</v>
@@ -1345,16 +1345,16 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-1.4442</v>
+        <v>-0.2557999999999985</v>
       </c>
       <c r="E12" t="n">
-        <v>-7.7867</v>
+        <v>-6.5986</v>
       </c>
       <c r="F12" t="n">
-        <v>6.342700000000001</v>
+        <v>6.342799999999999</v>
       </c>
       <c r="G12" t="n">
-        <v>-6.775699999999999</v>
+        <v>-6.7757</v>
       </c>
       <c r="H12" t="n">
         <v>1.359300000000001</v>
@@ -1390,13 +1390,13 @@
         <v>14.6885</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.5059</v>
+        <v>0.6824</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.3382000000000002</v>
+        <v>0.8498000000000001</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.1676</v>
+        <v>-0.1675999999999999</v>
       </c>
       <c r="V12" t="n">
         <v>0.9412000000000003</v>
@@ -1411,7 +1411,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>L. GARCIA ORTIZ</t>
+          <t>M. CACHOPAS GIL PRATES</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1423,67 +1423,67 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>3.7282</v>
+        <v>3.7721</v>
       </c>
       <c r="E13" t="n">
-        <v>1.854</v>
+        <v>1.6384</v>
       </c>
       <c r="F13" t="n">
-        <v>1.8742</v>
+        <v>2.1336</v>
       </c>
       <c r="G13" t="n">
-        <v>2.6719</v>
+        <v>2.565</v>
       </c>
       <c r="H13" t="n">
-        <v>1.1862</v>
+        <v>1.6707</v>
       </c>
       <c r="I13" t="n">
-        <v>1.4857</v>
+        <v>0.8943</v>
       </c>
       <c r="J13" t="n">
-        <v>1.1012</v>
+        <v>1.5943</v>
       </c>
       <c r="K13" t="n">
-        <v>0.9799</v>
+        <v>2.3477</v>
       </c>
       <c r="L13" t="n">
-        <v>0.1212</v>
+        <v>-0.7534</v>
       </c>
       <c r="M13" t="n">
-        <v>1.5707</v>
+        <v>0.9707</v>
       </c>
       <c r="N13" t="n">
-        <v>0.2062</v>
+        <v>-0.677</v>
       </c>
       <c r="O13" t="n">
-        <v>1.3645</v>
+        <v>1.6477</v>
       </c>
       <c r="P13" t="n">
-        <v>-0.1958</v>
+        <v>-0.7834</v>
       </c>
       <c r="Q13" t="n">
-        <v>-0.3917</v>
+        <v>-2.1543</v>
       </c>
       <c r="R13" t="n">
-        <v>0.1958</v>
+        <v>1.3709</v>
       </c>
       <c r="S13" t="n">
-        <v>1.2521</v>
+        <v>-0.0457</v>
       </c>
       <c r="T13" t="n">
-        <v>1.1445</v>
+        <v>0.0982</v>
       </c>
       <c r="U13" t="n">
-        <v>0.1076</v>
+        <v>-0.1439</v>
       </c>
       <c r="V13" t="n">
-        <v>0</v>
+        <v>2.0362</v>
       </c>
       <c r="W13" t="n">
-        <v>0</v>
+        <v>2.1003</v>
       </c>
       <c r="X13" t="n">
-        <v>0</v>
+        <v>-0.0641</v>
       </c>
     </row>
     <row r="14">
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>3.6736</v>
+        <v>3.7225</v>
       </c>
       <c r="E14" t="n">
-        <v>3.7709</v>
+        <v>3.8732</v>
       </c>
       <c r="F14" t="n">
-        <v>-0.0973</v>
+        <v>-0.1507</v>
       </c>
       <c r="G14" t="n">
         <v>3.8481</v>
@@ -1546,13 +1546,13 @@
         <v>0.3917</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.095</v>
+        <v>-0.0462</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.4158</v>
+        <v>-0.3135</v>
       </c>
       <c r="U14" t="n">
-        <v>0.3208</v>
+        <v>0.2673</v>
       </c>
       <c r="V14" t="n">
         <v>-0.2754</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>3.6577</v>
+        <v>3.5821</v>
       </c>
       <c r="E15" t="n">
-        <v>1.3842</v>
+        <v>1.2818</v>
       </c>
       <c r="F15" t="n">
-        <v>2.2736</v>
+        <v>2.3003</v>
       </c>
       <c r="G15" t="n">
         <v>4.2127</v>
@@ -1624,13 +1624,13 @@
         <v>1.1751</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.2374</v>
+        <v>-0.313</v>
       </c>
       <c r="T15" t="n">
-        <v>0.0465</v>
+        <v>-0.0559</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.2839</v>
+        <v>-0.2572</v>
       </c>
       <c r="V15" t="n">
         <v>-0.1217</v>
@@ -1645,7 +1645,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>M. CACHOPAS GIL PRATES</t>
+          <t>L. GARCIA ORTIZ</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>2.8686</v>
+        <v>3.1142</v>
       </c>
       <c r="E16" t="n">
-        <v>0.9221</v>
+        <v>1.24</v>
       </c>
       <c r="F16" t="n">
-        <v>1.9465</v>
+        <v>1.8742</v>
       </c>
       <c r="G16" t="n">
-        <v>2.565</v>
+        <v>2.6719</v>
       </c>
       <c r="H16" t="n">
-        <v>1.6707</v>
+        <v>1.1862</v>
       </c>
       <c r="I16" t="n">
-        <v>0.8943</v>
+        <v>1.4857</v>
       </c>
       <c r="J16" t="n">
-        <v>1.5943</v>
+        <v>1.1012</v>
       </c>
       <c r="K16" t="n">
-        <v>2.3477</v>
+        <v>0.9799</v>
       </c>
       <c r="L16" t="n">
-        <v>-0.7534</v>
+        <v>0.1212</v>
       </c>
       <c r="M16" t="n">
-        <v>0.9707</v>
+        <v>1.5707</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.677</v>
+        <v>0.2062</v>
       </c>
       <c r="O16" t="n">
-        <v>1.6477</v>
+        <v>1.3645</v>
       </c>
       <c r="P16" t="n">
-        <v>-0.7834</v>
+        <v>-0.1958</v>
       </c>
       <c r="Q16" t="n">
-        <v>-2.1543</v>
+        <v>-0.3917</v>
       </c>
       <c r="R16" t="n">
-        <v>1.3709</v>
+        <v>0.1958</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.9492</v>
+        <v>0.6381</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.6181</v>
+        <v>0.5305</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.3311</v>
+        <v>0.1076</v>
       </c>
       <c r="V16" t="n">
-        <v>2.0362</v>
+        <v>0</v>
       </c>
       <c r="W16" t="n">
-        <v>2.1003</v>
+        <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>-0.0641</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>C. VALDES ALVAREZ</t>
+          <t>A. IGLESIAS CAMINO</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,64 +1735,64 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>2.1548</v>
+        <v>1.4691</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.083</v>
+        <v>0.5758</v>
       </c>
       <c r="F17" t="n">
-        <v>2.2378</v>
+        <v>0.8933</v>
       </c>
       <c r="G17" t="n">
-        <v>-1.0166</v>
+        <v>2.9955</v>
       </c>
       <c r="H17" t="n">
-        <v>-1.8405</v>
+        <v>-0.5458</v>
       </c>
       <c r="I17" t="n">
-        <v>0.8239</v>
+        <v>3.5413</v>
       </c>
       <c r="J17" t="n">
-        <v>-0.8999</v>
+        <v>3.6466</v>
       </c>
       <c r="K17" t="n">
-        <v>-1.026</v>
+        <v>-0.0052</v>
       </c>
       <c r="L17" t="n">
-        <v>0.1261</v>
+        <v>3.6518</v>
       </c>
       <c r="M17" t="n">
-        <v>-0.1167</v>
+        <v>-0.6511</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.8145</v>
+        <v>-0.5406</v>
       </c>
       <c r="O17" t="n">
-        <v>0.6978</v>
+        <v>-0.1105</v>
       </c>
       <c r="P17" t="n">
-        <v>0.7834</v>
+        <v>-0.3917</v>
       </c>
       <c r="Q17" t="n">
-        <v>-0.9792</v>
+        <v>-1.9585</v>
       </c>
       <c r="R17" t="n">
-        <v>1.7626</v>
+        <v>1.5668</v>
       </c>
       <c r="S17" t="n">
-        <v>2.5097</v>
+        <v>-0.3471</v>
       </c>
       <c r="T17" t="n">
-        <v>1.7962</v>
+        <v>-0.4464</v>
       </c>
       <c r="U17" t="n">
-        <v>0.7135</v>
+        <v>0.0993</v>
       </c>
       <c r="V17" t="n">
-        <v>-0.1217</v>
+        <v>-0.7875</v>
       </c>
       <c r="W17" t="n">
-        <v>0</v>
+        <v>-0.6659</v>
       </c>
       <c r="X17" t="n">
         <v>-0.1217</v>
@@ -1801,7 +1801,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A. IGLESIAS CAMINO</t>
+          <t>C. VALDES ALVAREZ</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,64 +1813,64 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>0.8192</v>
+        <v>0.4594</v>
       </c>
       <c r="E18" t="n">
-        <v>0.1665</v>
+        <v>-1.618</v>
       </c>
       <c r="F18" t="n">
-        <v>0.6526999999999999</v>
+        <v>2.0774</v>
       </c>
       <c r="G18" t="n">
-        <v>2.9955</v>
+        <v>-1.0166</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.5458</v>
+        <v>-1.8405</v>
       </c>
       <c r="I18" t="n">
-        <v>3.5413</v>
+        <v>0.8239</v>
       </c>
       <c r="J18" t="n">
-        <v>3.6466</v>
+        <v>-0.8999</v>
       </c>
       <c r="K18" t="n">
-        <v>-0.0052</v>
+        <v>-1.026</v>
       </c>
       <c r="L18" t="n">
-        <v>3.6518</v>
+        <v>0.1261</v>
       </c>
       <c r="M18" t="n">
-        <v>-0.6511</v>
+        <v>-0.1167</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.5406</v>
+        <v>-0.8145</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.1105</v>
+        <v>0.6978</v>
       </c>
       <c r="P18" t="n">
-        <v>-0.3917</v>
+        <v>0.7834</v>
       </c>
       <c r="Q18" t="n">
-        <v>-1.9585</v>
+        <v>-0.9792</v>
       </c>
       <c r="R18" t="n">
-        <v>1.5668</v>
+        <v>1.7626</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.9971</v>
+        <v>0.8143</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.8557</v>
+        <v>0.2611</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.1413</v>
+        <v>0.5531</v>
       </c>
       <c r="V18" t="n">
-        <v>-0.7875</v>
+        <v>-0.1217</v>
       </c>
       <c r="W18" t="n">
-        <v>-0.6659</v>
+        <v>0</v>
       </c>
       <c r="X18" t="n">
         <v>-0.1217</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.6606</v>
+        <v>-0.3803</v>
       </c>
       <c r="E19" t="n">
-        <v>-1.9261</v>
+        <v>-1.619</v>
       </c>
       <c r="F19" t="n">
-        <v>1.2654</v>
+        <v>1.2387</v>
       </c>
       <c r="G19" t="n">
         <v>-0.4075</v>
@@ -1936,13 +1936,13 @@
         <v>1.7626</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.8365</v>
+        <v>-0.5562</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.4288</v>
+        <v>-0.1218</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.4077</v>
+        <v>-0.4345</v>
       </c>
       <c r="V19" t="n">
         <v>-0.7875</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-2.4902</v>
+        <v>-2.4856</v>
       </c>
       <c r="E20" t="n">
-        <v>0.5358000000000001</v>
+        <v>0.4335</v>
       </c>
       <c r="F20" t="n">
-        <v>-3.026</v>
+        <v>-2.9191</v>
       </c>
       <c r="G20" t="n">
         <v>-0.4813</v>
@@ -2014,13 +2014,13 @@
         <v>0.7834</v>
       </c>
       <c r="S20" t="n">
-        <v>0.0119</v>
+        <v>0.0165</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.0129</v>
+        <v>-0.1153</v>
       </c>
       <c r="U20" t="n">
-        <v>0.0248</v>
+        <v>0.1317</v>
       </c>
       <c r="V20" t="n">
         <v>-1.8249</v>
@@ -2035,7 +2035,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A. BLANCO BLANCO</t>
+          <t>A. BELLON LOPEZ</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,73 +2047,73 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-3.7653</v>
+        <v>-3.1965</v>
       </c>
       <c r="E21" t="n">
-        <v>-2.074</v>
+        <v>-5.1466</v>
       </c>
       <c r="F21" t="n">
-        <v>-1.6912</v>
+        <v>1.9501</v>
       </c>
       <c r="G21" t="n">
-        <v>-0.6153999999999999</v>
+        <v>-2.7685</v>
       </c>
       <c r="H21" t="n">
-        <v>-0.1204</v>
+        <v>-1.4849</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.495</v>
+        <v>-1.2836</v>
       </c>
       <c r="J21" t="n">
-        <v>0.1221</v>
+        <v>-3.9309</v>
       </c>
       <c r="K21" t="n">
-        <v>0.08169999999999999</v>
+        <v>-1.2828</v>
       </c>
       <c r="L21" t="n">
-        <v>0.0404</v>
+        <v>-2.6481</v>
       </c>
       <c r="M21" t="n">
-        <v>-0.7375</v>
+        <v>1.1624</v>
       </c>
       <c r="N21" t="n">
         <v>-0.2021</v>
       </c>
       <c r="O21" t="n">
-        <v>-0.5354</v>
+        <v>1.3645</v>
       </c>
       <c r="P21" t="n">
-        <v>-1.9585</v>
+        <v>-0.9792</v>
       </c>
       <c r="Q21" t="n">
-        <v>-1.9585</v>
+        <v>-1.3709</v>
       </c>
       <c r="R21" t="n">
-        <v>0</v>
+        <v>0.3917</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.6407</v>
+        <v>0.2183</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.2376</v>
+        <v>0.1553</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.403</v>
+        <v>0.0631</v>
       </c>
       <c r="V21" t="n">
-        <v>-0.5507</v>
+        <v>0.3329</v>
       </c>
       <c r="W21" t="n">
         <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>-0.5507</v>
+        <v>0.3329</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A. BELLON LOPEZ</t>
+          <t>A. BLANCO BLANCO</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,67 +2125,67 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-3.7884</v>
+        <v>-3.5873</v>
       </c>
       <c r="E22" t="n">
-        <v>-5.6583</v>
+        <v>-1.8694</v>
       </c>
       <c r="F22" t="n">
-        <v>1.8699</v>
+        <v>-1.718</v>
       </c>
       <c r="G22" t="n">
-        <v>-2.7685</v>
+        <v>-0.6153999999999999</v>
       </c>
       <c r="H22" t="n">
-        <v>-1.4849</v>
+        <v>-0.1204</v>
       </c>
       <c r="I22" t="n">
-        <v>-1.2836</v>
+        <v>-0.495</v>
       </c>
       <c r="J22" t="n">
-        <v>-3.9309</v>
+        <v>0.1221</v>
       </c>
       <c r="K22" t="n">
-        <v>-1.2828</v>
+        <v>0.08169999999999999</v>
       </c>
       <c r="L22" t="n">
-        <v>-2.6481</v>
+        <v>0.0404</v>
       </c>
       <c r="M22" t="n">
-        <v>1.1624</v>
+        <v>-0.7375</v>
       </c>
       <c r="N22" t="n">
         <v>-0.2021</v>
       </c>
       <c r="O22" t="n">
-        <v>1.3645</v>
+        <v>-0.5354</v>
       </c>
       <c r="P22" t="n">
-        <v>-0.9792</v>
+        <v>-1.9585</v>
       </c>
       <c r="Q22" t="n">
-        <v>-1.3709</v>
+        <v>-1.9585</v>
       </c>
       <c r="R22" t="n">
-        <v>0.3917</v>
+        <v>0</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.3735</v>
+        <v>-0.4627</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.3564</v>
+        <v>-0.0329</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.0171</v>
+        <v>-0.4298</v>
       </c>
       <c r="V22" t="n">
-        <v>0.3329</v>
+        <v>-0.5507</v>
       </c>
       <c r="W22" t="n">
         <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>0.3329</v>
+        <v>-0.5507</v>
       </c>
     </row>
     <row r="23">
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-4.7538</v>
+        <v>-5.0257</v>
       </c>
       <c r="E23" t="n">
-        <v>-5.2347</v>
+        <v>-5.1324</v>
       </c>
       <c r="F23" t="n">
-        <v>0.481</v>
+        <v>0.1067</v>
       </c>
       <c r="G23" t="n">
         <v>-4.2283</v>
@@ -2248,13 +2248,13 @@
         <v>0.3917</v>
       </c>
       <c r="S23" t="n">
-        <v>0.8615</v>
+        <v>0.5896</v>
       </c>
       <c r="T23" t="n">
-        <v>0.1059</v>
+        <v>0.2082</v>
       </c>
       <c r="U23" t="n">
-        <v>0.7556</v>
+        <v>0.3814</v>
       </c>
       <c r="V23" t="n">
         <v>1.159</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>1.4438</v>
+        <v>1.443999999999999</v>
       </c>
       <c r="E24" t="n">
-        <v>-6.342599999999999</v>
+        <v>-6.3427</v>
       </c>
       <c r="F24" t="n">
-        <v>7.7866</v>
+        <v>7.7865</v>
       </c>
       <c r="G24" t="n">
         <v>6.7756</v>
@@ -2314,7 +2314,7 @@
         <v>-5.0726</v>
       </c>
       <c r="O24" t="n">
-        <v>4.9315</v>
+        <v>4.931500000000001</v>
       </c>
       <c r="P24" t="n">
         <v>-4.8961</v>
@@ -2326,16 +2326,16 @@
         <v>9.792299999999999</v>
       </c>
       <c r="S24" t="n">
-        <v>0.5057999999999998</v>
+        <v>0.5059</v>
       </c>
       <c r="T24" t="n">
-        <v>0.1678000000000001</v>
+        <v>0.1675</v>
       </c>
       <c r="U24" t="n">
-        <v>0.3382000000000001</v>
+        <v>0.3381000000000001</v>
       </c>
       <c r="V24" t="n">
-        <v>-0.9413000000000002</v>
+        <v>-0.9412999999999998</v>
       </c>
       <c r="W24" t="n">
         <v>1.2616</v>
